--- a/quizzes/026_pharmacology_and_pathology_quiz--quizzes.xlsx
+++ b/quizzes/026_pharmacology_and_pathology_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1892,8 +1892,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1955,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{3:_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{3: 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1989,12 +1989,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2023,12 +2023,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2074,12 +2074,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2091,12 +2091,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2227,12 +2227,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2278,12 +2278,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2312,12 +2312,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2329,12 +2329,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2499,12 +2499,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2567,12 +2567,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2652,12 +2652,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2703,12 +2703,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2720,12 +2720,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2737,12 +2737,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2754,12 +2754,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2856,12 +2856,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3077,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3417,12 +3417,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3502,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3655,12 +3655,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{1:_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{1: 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{2:_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{2: 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
